--- a/important_mails_2026-08-29.xlsx
+++ b/important_mails_2026-08-29.xlsx
@@ -1787,7 +1787,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>付款/资金类</t>
+          <t>产品链接/合规类</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -1802,122 +1802,21 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Sat, 22 Aug 2026 17:14:31 +0000</t>
+          <t>Thu, 27 Aug 2026 15:47:49 +0000</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+          <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>Tu pago está en camino</t>
+          <t>Seller News: August 2026</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr"/>
       <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>96
-This title will display on mobile devices
- ¡Enhorabuena! El pago está de camino y llegará pronto.
- El pago está en camino
-Enhorabuena, Weihai EU. Tu pago está en camino y te llegará en un plazo de tres a cinco días.
-El 08/22/26 17:14 WEST, iniciamos una transferencia a tu método de pago (cuenta bancaria terminado en 229) por un importe de €
- 646,15.
- Si el importe es inferior a lo esperado, ten en cuenta las siguientes preguntas:
- ¿Tienes saldo no disponible en tu cuenta de vendedor? Puede que hayamos reservado algo de dinero para posibles devoluciones, reclamaciones o reversiones de cargo de clientes. En este caso, el saldo de cierre de tu informe de pagos te mostrará el saldo no disponible en reserva.
- ¿Cubren tus ventas las tarifas de Amazon y las devoluciones del periodo de liquidación? El importe del pago refleja las ventas que has hecho y las tarifas de venta aplicadas tanto a dichas ventas como a cualquier promoción o servicio que hayas utilizado. Te recomendamos que revises tu informe de pagos en "Informes" de Seller Central para conocer el saldo de cierre.
-Para más información sobre los informes de pagos en Seller Central, visita nuestro curso oficial.
-Te deseamos un éx</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>付款/资金类</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>Sat, 22 Aug 2026 17:14:20 +0000</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>Your payment is on the way</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr"/>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>96
-This title will display on mobile devices
- Congratulations! Your payment is on the way and will arrive soon.
- Disbursement Attempted
-Congratulations Weihai EU! Your payment is on the way and will arrive within three to five days.
-On 08/22/26 17:14 CEST, we initiated a transfer to your payment method (bank account ending in 229) in the amount of €
- 397.48.
- If the amount is less than expected, here are a few questions to consider:
- Do you have an unavailable balance? Amazon might be reserving money to cover potential returns, claims, or chargebacks from buyers. If this is the case, the closing balance in your Payment Report will display the unavailable balance that is reserved.
- Did your sales cover all fees and returns for this statement period? The payment amount reflects sales activities, selling fees, and fees for promotions or services. We recommend reviewing your Payment Report under the Reports tab in Seller Central to understand your closing balance.
-To learn more about Payment Reports in Seller Central, please visit our official course.
-We wish you continued success!
-Thank you for selling in the Amazon store,
-Amazon Services
-Help us improve your payment experience on Ama</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>产品链接/合规类</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>Thu, 27 Aug 2026 15:47:49 +0000</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>Seller News: August 2026</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr"/>
-      <c r="H30" s="2" t="inlineStr">
         <is>
           <t>Seller News: August 2026
  96
@@ -1927,39 +1826,39 @@
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>Thu, 27 Aug 2026 08:15:11 +0000</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
+      <c r="F29" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr"/>
-      <c r="H31" s="2" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr"/>
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -1978,39 +1877,39 @@
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>Thu, 27 Aug 2026 08:11:05 +0000</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr"/>
-      <c r="H32" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr"/>
+      <c r="H30" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -2029,39 +1928,39 @@
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>Wed, 26 Aug 2026 14:08:01 +0000</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="E31" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
+      <c r="F31" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G33" s="2" t="inlineStr"/>
-      <c r="H33" s="2" t="inlineStr">
+      <c r="G31" s="2" t="inlineStr"/>
+      <c r="H31" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Submit product safety documentation to reactivate listings
@@ -2079,39 +1978,39 @@
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>Wed, 26 Aug 2026 08:11:28 +0000</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr"/>
-      <c r="H34" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr"/>
+      <c r="H32" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -2130,39 +2029,39 @@
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
         <is>
           <t>Wed, 26 Aug 2026 08:08:21 +0000</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="E33" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
+      <c r="F33" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G35" s="2" t="inlineStr"/>
-      <c r="H35" s="2" t="inlineStr">
+      <c r="G33" s="2" t="inlineStr"/>
+      <c r="H33" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -2181,39 +2080,39 @@
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>Wed, 26 Aug 2026 08:07:34 +0000</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr"/>
-      <c r="H36" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr"/>
+      <c r="H34" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -2232,39 +2131,39 @@
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
         <is>
           <t>Wed, 26 Aug 2026 08:07:29 +0000</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="E35" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
+      <c r="F35" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr"/>
-      <c r="H37" s="2" t="inlineStr">
+      <c r="G35" s="2" t="inlineStr"/>
+      <c r="H35" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -2283,39 +2182,39 @@
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
         <is>
           <t>Tue, 25 Aug 2026 14:07:29 +0000</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="E36" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr"/>
-      <c r="H38" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr"/>
+      <c r="H36" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Submit product safety documentation to reactivate listings
@@ -2333,39 +2232,39 @@
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
+      <c r="B37" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
         <is>
           <t>Tue, 25 Aug 2026 13:07:04 +0000</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="E37" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr">
+      <c r="F37" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G39" s="2" t="inlineStr"/>
-      <c r="H39" s="2" t="inlineStr">
+      <c r="G37" s="2" t="inlineStr"/>
+      <c r="H37" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Hello Weihai CA,
@@ -2384,39 +2283,39 @@
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
         <is>
           <t>Tue, 25 Aug 2026 09:06:58 +0000</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="E38" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr">
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G40" s="2" t="inlineStr"/>
-      <c r="H40" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr"/>
+      <c r="H38" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -2434,39 +2333,39 @@
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
+      <c r="B39" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
         <is>
           <t>Mon, 24 Aug 2026 16:31:11 +0000</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="E39" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Support &lt;merch.service05@amazon.co.uk&gt;</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
+      <c r="F39" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 13205236962] 【需立即行动】请通过亚马逊认可的TIC服务商完成儿童玩具合规</t>
         </is>
       </c>
-      <c r="G41" s="2" t="inlineStr"/>
-      <c r="H41" s="2" t="inlineStr">
+      <c r="G39" s="2" t="inlineStr"/>
+      <c r="H39" s="2" t="inlineStr">
         <is>
           <t>96
 RE:[CASE 13205236962] 【需立即行动】请通过亚马逊认可的TIC服务商完成儿童玩具合规
@@ -2501,40 +2400,40 @@
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t>Mon, 24 Aug 2026 06:47:57 +0000</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.de" &lt;cscompliance-docreview-seller@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr">
+      <c r="F40" s="2" t="inlineStr">
         <is>
           <t>SELLER: A1UYGOR4ZW45MU, ASIN: B0GYPZ58JY, MARKETPLACE:
  A1PA6795UKMFR9 - SPO - Seller Partner Outreach - Document Review</t>
         </is>
       </c>
-      <c r="G42" s="2" t="inlineStr"/>
-      <c r="H42" s="2" t="inlineStr">
+      <c r="G40" s="2" t="inlineStr"/>
+      <c r="H40" s="2" t="inlineStr">
         <is>
           <t>96
 SELLER: A1UYGOR4ZW45MU, ASIN: B0GYPZ58JY, MARKETPLACE: A1PA6795UKMFR9 - SPO - Seller Partner Outreach - Document Review
@@ -2552,39 +2451,39 @@
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
+      <c r="B41" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
         <is>
           <t>Sun, 23 Aug 2026 16:08:02 +0000</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="E41" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr">
+      <c r="F41" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G43" s="2" t="inlineStr"/>
-      <c r="H43" s="2" t="inlineStr">
+      <c r="G41" s="2" t="inlineStr"/>
+      <c r="H41" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -2602,89 +2501,39 @@
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>产品链接/合规类</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>Sat, 22 Aug 2026 23:14:29 +0000</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 27 Aug 2026 08:15:03 +0000</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>Submit product safety documentation to reactivate listings</t>
-        </is>
-      </c>
-      <c r="G44" s="2" t="inlineStr"/>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t>96
- Submit product safety documentation to reactivate listings
- Hello Weihai EU,
- Some of your listings have been deactivated due to missing mandatory compliance requirements for your products. Review the details and next steps below. The affected listings are shown at the end of this email.
- Why is this happening?
- We are taking this action because these products are missing mandatory compliance information. Review our Product safety and compliance help page for information on applicable laws, regulations and Amazon policies. We leveraged a combination of automated means and expert human review to identify this issue and make this decision.
- The table at the end of this email provides product-specific compliance requirements.
- How do I reactivate my listing?
- To provide the required compliance information, go to your Account Health page and locate the product compliance requests:
--
- If you have the required documentation, follow the instructions to submit your compliance documents. We will only reinstate products that fulfil the compliance requirements.
--
- If you believe that your products are exempt from these requirements, submit documentation demonstrating why they are not subj</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
-        <is>
-          <t>Thu, 27 Aug 2026 08:15:03 +0000</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F45" s="2" t="inlineStr">
+      <c r="F42" s="2" t="inlineStr">
         <is>
           <t>Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu niedopuszczenia do dezaktywacji oferty</t>
         </is>
       </c>
-      <c r="G45" s="2" t="inlineStr"/>
-      <c r="H45" s="2" t="inlineStr">
+      <c r="G42" s="2" t="inlineStr"/>
+      <c r="H42" s="2" t="inlineStr">
         <is>
           <t>96
  Dzień dobry Weihai EU,
@@ -2701,39 +2550,39 @@
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
         <is>
           <t>Thu, 27 Aug 2026 08:13:08 +0000</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="E43" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr">
+      <c r="F43" s="2" t="inlineStr">
         <is>
           <t>Skicka in produktsäkerhetsdokumentation för att undvika att produktposterna inaktiveras</t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr"/>
-      <c r="H46" s="2" t="inlineStr">
+      <c r="G43" s="2" t="inlineStr"/>
+      <c r="H43" s="2" t="inlineStr">
         <is>
           <t>96
  Hej Weihai EU!
@@ -2751,40 +2600,40 @@
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C47" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="inlineStr">
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
         <is>
           <t>Thu, 27 Aug 2026 08:10:41 +0000</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
+      <c r="E44" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F47" s="2" t="inlineStr">
+      <c r="F44" s="2" t="inlineStr">
         <is>
           <t>Invia la documentazione sulla sicurezza del prodotto per evitare la
  disattivazione dell'offerta</t>
         </is>
       </c>
-      <c r="G47" s="2" t="inlineStr"/>
-      <c r="H47" s="2" t="inlineStr">
+      <c r="G44" s="2" t="inlineStr"/>
+      <c r="H44" s="2" t="inlineStr">
         <is>
           <t>96
  Gentile Weihai EU,
@@ -2802,39 +2651,39 @@
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr">
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
         <is>
           <t>Thu, 27 Aug 2026 08:08:46 +0000</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr">
+      <c r="E45" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F48" s="2" t="inlineStr">
+      <c r="F45" s="2" t="inlineStr">
         <is>
           <t>Soumettre la documentation de sécurité des produits pour éviter la désactivation des mises en vente</t>
         </is>
       </c>
-      <c r="G48" s="2" t="inlineStr"/>
-      <c r="H48" s="2" t="inlineStr">
+      <c r="G45" s="2" t="inlineStr"/>
+      <c r="H45" s="2" t="inlineStr">
         <is>
           <t>96
  Bonjour Weihai EU,
@@ -2852,39 +2701,39 @@
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C49" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr">
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
         <is>
           <t>Thu, 27 Aug 2026 07:12:52 +0000</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr">
+      <c r="E46" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F49" s="2" t="inlineStr">
+      <c r="F46" s="2" t="inlineStr">
         <is>
           <t>Presenta la documentación sobre seguridad del producto para evitar la desactivación de los listings</t>
         </is>
       </c>
-      <c r="G49" s="2" t="inlineStr"/>
-      <c r="H49" s="2" t="inlineStr">
+      <c r="G46" s="2" t="inlineStr"/>
+      <c r="H46" s="2" t="inlineStr">
         <is>
           <t>96
  Hola, Weihai EU:
@@ -2902,40 +2751,40 @@
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B50" s="2" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
         <is>
           <t>Thu, 27 Aug 2026 07:12:42 +0000</t>
         </is>
       </c>
-      <c r="E50" s="2" t="inlineStr">
+      <c r="E47" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F50" s="2" t="inlineStr">
+      <c r="F47" s="2" t="inlineStr">
         <is>
           <t>Dien productveiligheidsdocumentatie in om de deactivering van de
  productvermelding te voorkomen</t>
         </is>
       </c>
-      <c r="G50" s="2" t="inlineStr"/>
-      <c r="H50" s="2" t="inlineStr">
+      <c r="G47" s="2" t="inlineStr"/>
+      <c r="H47" s="2" t="inlineStr">
         <is>
           <t>96
  Hallo Weihai EU,
@@ -2953,39 +2802,39 @@
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B51" s="2" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C51" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="inlineStr">
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
         <is>
           <t>Wed, 26 Aug 2026 10:00:43 +0000</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr">
+      <c r="E48" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Support &lt;merch.service05@amazon.pl&gt;</t>
         </is>
       </c>
-      <c r="F51" s="2" t="inlineStr">
+      <c r="F48" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 13214292782] 创建或更新 ASIN 变体</t>
         </is>
       </c>
-      <c r="G51" s="2" t="inlineStr"/>
-      <c r="H51" s="2" t="inlineStr">
+      <c r="G48" s="2" t="inlineStr"/>
+      <c r="H48" s="2" t="inlineStr">
         <is>
           <t>96
 RE:[CASE 13214292782] 创建或更新 ASIN 变体
@@ -3019,39 +2868,39 @@
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B52" s="2" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
         <is>
           <t>Wed, 26 Aug 2026 10:00:35 +0000</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr">
+      <c r="E49" s="2" t="inlineStr">
         <is>
           <t>Assistenza venditori Amazon &lt;merch.service05@amazon.it&gt;</t>
         </is>
       </c>
-      <c r="F52" s="2" t="inlineStr">
+      <c r="F49" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 13214194642] 创建或更新 ASIN 变体</t>
         </is>
       </c>
-      <c r="G52" s="2" t="inlineStr"/>
-      <c r="H52" s="2" t="inlineStr">
+      <c r="G49" s="2" t="inlineStr"/>
+      <c r="H49" s="2" t="inlineStr">
         <is>
           <t>96
 RE:[CASE 13214194642] 创建或更新 ASIN 变体
@@ -3084,39 +2933,39 @@
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B53" s="2" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C53" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="inlineStr">
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
         <is>
           <t>Wed, 26 Aug 2026 08:59:03 +0000</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr">
+      <c r="E50" s="2" t="inlineStr">
         <is>
           <t>Asistencia al Vendedor de Amazon &lt;merch.service05@amazon.es&gt;</t>
         </is>
       </c>
-      <c r="F53" s="2" t="inlineStr">
+      <c r="F50" s="2" t="inlineStr">
         <is>
           <t>Resolución del número de caso: 13214253602</t>
         </is>
       </c>
-      <c r="G53" s="2" t="inlineStr"/>
-      <c r="H53" s="2" t="inlineStr">
+      <c r="G50" s="2" t="inlineStr"/>
+      <c r="H50" s="2" t="inlineStr">
         <is>
           <t>96
 Resolución del número de caso: 13214253602
@@ -3136,39 +2985,39 @@
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B54" s="2" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C54" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="inlineStr">
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
         <is>
           <t>Wed, 26 Aug 2026 08:11:26 +0000</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="E51" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F54" s="2" t="inlineStr">
+      <c r="F51" s="2" t="inlineStr">
         <is>
           <t>Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu niedopuszczenia do dezaktywacji oferty</t>
         </is>
       </c>
-      <c r="G54" s="2" t="inlineStr"/>
-      <c r="H54" s="2" t="inlineStr">
+      <c r="G51" s="2" t="inlineStr"/>
+      <c r="H51" s="2" t="inlineStr">
         <is>
           <t>96
  Dzień dobry Weihai EU,
@@ -3185,39 +3034,39 @@
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B55" s="2" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C55" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr">
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
         <is>
           <t>Wed, 26 Aug 2026 08:10:20 +0000</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr">
+      <c r="E52" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F55" s="2" t="inlineStr">
+      <c r="F52" s="2" t="inlineStr">
         <is>
           <t>Skicka in produktsäkerhetsdokumentation för att undvika att produktposterna inaktiveras</t>
         </is>
       </c>
-      <c r="G55" s="2" t="inlineStr"/>
-      <c r="H55" s="2" t="inlineStr">
+      <c r="G52" s="2" t="inlineStr"/>
+      <c r="H52" s="2" t="inlineStr">
         <is>
           <t>96
  Hej Weihai EU!
@@ -3235,40 +3084,40 @@
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B56" s="2" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C56" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr">
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
         <is>
           <t>Wed, 26 Aug 2026 08:09:31 +0000</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
+      <c r="E53" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F56" s="2" t="inlineStr">
+      <c r="F53" s="2" t="inlineStr">
         <is>
           <t>Invia la documentazione sulla sicurezza del prodotto per evitare la
  disattivazione dell'offerta</t>
         </is>
       </c>
-      <c r="G56" s="2" t="inlineStr"/>
-      <c r="H56" s="2" t="inlineStr">
+      <c r="G53" s="2" t="inlineStr"/>
+      <c r="H53" s="2" t="inlineStr">
         <is>
           <t>96
  Gentile Weihai EU,
@@ -3286,39 +3135,39 @@
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B57" s="2" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C57" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr">
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
         <is>
           <t>Wed, 26 Aug 2026 08:07:50 +0000</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="E54" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F57" s="2" t="inlineStr">
+      <c r="F54" s="2" t="inlineStr">
         <is>
           <t>Soumettre la documentation de sécurité des produits pour éviter la désactivation des mises en vente</t>
         </is>
       </c>
-      <c r="G57" s="2" t="inlineStr"/>
-      <c r="H57" s="2" t="inlineStr">
+      <c r="G54" s="2" t="inlineStr"/>
+      <c r="H54" s="2" t="inlineStr">
         <is>
           <t>96
  Bonjour Weihai EU,
@@ -3336,39 +3185,39 @@
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B58" s="2" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C58" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr">
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
         <is>
           <t>Wed, 26 Aug 2026 07:12:00 +0000</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="E55" s="2" t="inlineStr">
         <is>
           <t>亚马逊开店服务 &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F58" s="2" t="inlineStr">
+      <c r="F55" s="2" t="inlineStr">
         <is>
           <t>提交商品安全文件以避免商品被停售</t>
         </is>
       </c>
-      <c r="G58" s="2" t="inlineStr"/>
-      <c r="H58" s="2" t="inlineStr">
+      <c r="G55" s="2" t="inlineStr"/>
+      <c r="H55" s="2" t="inlineStr">
         <is>
           <t>96
  尊敬的 Weihai EU：
@@ -3411,40 +3260,40 @@
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B59" s="2" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C59" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="inlineStr">
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
         <is>
           <t>Wed, 26 Aug 2026 07:10:48 +0000</t>
         </is>
       </c>
-      <c r="E59" s="2" t="inlineStr">
+      <c r="E56" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F59" s="2" t="inlineStr">
+      <c r="F56" s="2" t="inlineStr">
         <is>
           <t>Dien productveiligheidsdocumentatie in om de deactivering van de
  productvermelding te voorkomen</t>
         </is>
       </c>
-      <c r="G59" s="2" t="inlineStr"/>
-      <c r="H59" s="2" t="inlineStr">
+      <c r="G56" s="2" t="inlineStr"/>
+      <c r="H56" s="2" t="inlineStr">
         <is>
           <t>96
  Hallo Weihai EU,
@@ -3462,39 +3311,39 @@
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B60" s="2" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C60" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr">
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
         <is>
           <t>Wed, 26 Aug 2026 07:10:45 +0000</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr">
+      <c r="E57" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F60" s="2" t="inlineStr">
+      <c r="F57" s="2" t="inlineStr">
         <is>
           <t>Presenta la documentación sobre seguridad del producto para evitar la desactivación de los listings</t>
         </is>
       </c>
-      <c r="G60" s="2" t="inlineStr"/>
-      <c r="H60" s="2" t="inlineStr">
+      <c r="G57" s="2" t="inlineStr"/>
+      <c r="H57" s="2" t="inlineStr">
         <is>
           <t>96
  Hola, Weihai EU:
@@ -3512,39 +3361,39 @@
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B61" s="2" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C61" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D61" s="2" t="inlineStr">
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
         <is>
           <t>Tue, 25 Aug 2026 13:09:12 +0000</t>
         </is>
       </c>
-      <c r="E61" s="2" t="inlineStr">
+      <c r="E58" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F61" s="2" t="inlineStr">
+      <c r="F58" s="2" t="inlineStr">
         <is>
           <t>New Selection Program benefits are now live</t>
         </is>
       </c>
-      <c r="G61" s="2" t="inlineStr"/>
-      <c r="H61" s="2" t="inlineStr">
+      <c r="G58" s="2" t="inlineStr"/>
+      <c r="H58" s="2" t="inlineStr">
         <is>
           <t>New Selection Program (2026) benefits are now live
  New Selection Program benefits are now live
@@ -3560,39 +3409,39 @@
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B62" s="2" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C62" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D62" s="2" t="inlineStr">
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
         <is>
           <t>Tue, 25 Aug 2026 00:16:32 +0000</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr">
+      <c r="E59" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F62" s="2" t="inlineStr">
+      <c r="F59" s="2" t="inlineStr">
         <is>
           <t>FBA Grade and Resell is now available in Canada</t>
         </is>
       </c>
-      <c r="G62" s="2" t="inlineStr"/>
-      <c r="H62" s="2" t="inlineStr">
+      <c r="G59" s="2" t="inlineStr"/>
+      <c r="H59" s="2" t="inlineStr">
         <is>
           <t>96
  A new way to recover value from your FBA returns
@@ -3613,40 +3462,40 @@
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B63" s="2" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C63" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="inlineStr">
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
         <is>
           <t>Mon, 24 Aug 2026 09:57:03 +0000</t>
         </is>
       </c>
-      <c r="E63" s="2" t="inlineStr">
+      <c r="E60" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F63" s="2" t="inlineStr">
+      <c r="F60" s="2" t="inlineStr">
         <is>
           <t>Activeer je aanbod voor Nederland voor Pan-EU FBA op uiterlijk 3
  september</t>
         </is>
       </c>
-      <c r="G63" s="2" t="inlineStr"/>
-      <c r="H63" s="2" t="inlineStr">
+      <c r="G60" s="2" t="inlineStr"/>
+      <c r="H60" s="2" t="inlineStr">
         <is>
           <t>Voor Pan-EU FBA zijn aanbiedingen in Nederland vereist
  96
@@ -3657,39 +3506,39 @@
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
+      <c r="B61" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C64" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr">
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
         <is>
           <t>Thu, 27 Aug 2026 15:43:49 +0000</t>
         </is>
       </c>
-      <c r="E64" s="2" t="inlineStr">
+      <c r="E61" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Newsletter &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F64" s="2" t="inlineStr">
+      <c r="F61" s="2" t="inlineStr">
         <is>
           <t>Seller News: August 2026</t>
         </is>
       </c>
-      <c r="G64" s="2" t="inlineStr"/>
-      <c r="H64" s="2" t="inlineStr">
+      <c r="G61" s="2" t="inlineStr"/>
+      <c r="H61" s="2" t="inlineStr">
         <is>
           <t>Seller News: August 2026
  96
@@ -3699,40 +3548,40 @@
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="2" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
+      <c r="B62" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C65" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D65" s="2" t="inlineStr">
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
         <is>
           <t>Wed, 26 Aug 2026 14:03:19 +0000</t>
         </is>
       </c>
-      <c r="E65" s="2" t="inlineStr">
+      <c r="E62" s="2" t="inlineStr">
         <is>
           <t>Amazon Multichannel Fulfillment Team &lt;multichannelfulfillment@supplychain.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F65" s="2" t="inlineStr">
+      <c r="F62" s="2" t="inlineStr">
         <is>
           <t>Early access: Bring the trust of Prime to your ecommerce site with
  MCF</t>
         </is>
       </c>
-      <c r="G65" s="2" t="inlineStr"/>
-      <c r="H65" s="2" t="inlineStr">
+      <c r="G62" s="2" t="inlineStr"/>
+      <c r="H62" s="2" t="inlineStr">
         <is>
           <t>Early access: Bring the trust of Prime to your ecommerce site with MCF
 Hi there,
@@ -3746,39 +3595,39 @@
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C66" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr">
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
         <is>
           <t>Sat, 22 Aug 2026 03:28:54 +0000</t>
         </is>
       </c>
-      <c r="E66" s="2" t="inlineStr">
+      <c r="E63" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F66" s="2" t="inlineStr">
+      <c r="F63" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G66" s="2" t="inlineStr"/>
-      <c r="H66" s="2" t="inlineStr">
+      <c r="G63" s="2" t="inlineStr"/>
+      <c r="H63" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -3794,39 +3643,39 @@
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr">
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C67" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="inlineStr">
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
         <is>
           <t>Fri, 21 Aug 2026 16:10:20 +0000</t>
         </is>
       </c>
-      <c r="E67" s="2" t="inlineStr">
+      <c r="E64" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F67" s="2" t="inlineStr">
+      <c r="F64" s="2" t="inlineStr">
         <is>
           <t>Automated unfulfillable FBA inventory removal notification</t>
         </is>
       </c>
-      <c r="G67" s="2" t="inlineStr"/>
-      <c r="H67" s="2" t="inlineStr">
+      <c r="G64" s="2" t="inlineStr"/>
+      <c r="H64" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -3847,39 +3696,39 @@
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C68" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr">
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
         <is>
           <t>Thu, 20 Aug 2026 15:24:40 +0000</t>
         </is>
       </c>
-      <c r="E68" s="2" t="inlineStr">
+      <c r="E65" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F68" s="2" t="inlineStr">
+      <c r="F65" s="2" t="inlineStr">
         <is>
           <t>Automated unfulfillable FBA inventory removal notification</t>
         </is>
       </c>
-      <c r="G68" s="2" t="inlineStr"/>
-      <c r="H68" s="2" t="inlineStr">
+      <c r="G65" s="2" t="inlineStr"/>
+      <c r="H65" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -3900,39 +3749,39 @@
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr">
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C69" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="inlineStr">
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
         <is>
           <t>Thu, 20 Aug 2026 04:58:18 +0000</t>
         </is>
       </c>
-      <c r="E69" s="2" t="inlineStr">
+      <c r="E66" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F69" s="2" t="inlineStr">
+      <c r="F66" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G69" s="2" t="inlineStr"/>
-      <c r="H69" s="2" t="inlineStr">
+      <c r="G66" s="2" t="inlineStr"/>
+      <c r="H66" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -3948,39 +3797,39 @@
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C70" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="inlineStr">
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
         <is>
           <t>Wed, 19 Aug 2026 16:12:03 +0000</t>
         </is>
       </c>
-      <c r="E70" s="2" t="inlineStr">
+      <c r="E67" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F70" s="2" t="inlineStr">
+      <c r="F67" s="2" t="inlineStr">
         <is>
           <t>Automated unfulfillable FBA inventory removal notification</t>
         </is>
       </c>
-      <c r="G70" s="2" t="inlineStr"/>
-      <c r="H70" s="2" t="inlineStr">
+      <c r="G67" s="2" t="inlineStr"/>
+      <c r="H67" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -4001,39 +3850,39 @@
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="2" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C71" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D71" s="2" t="inlineStr">
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
         <is>
           <t>Tue, 18 Aug 2026 05:03:01 +0000</t>
         </is>
       </c>
-      <c r="E71" s="2" t="inlineStr">
+      <c r="E68" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F71" s="2" t="inlineStr">
+      <c r="F68" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G71" s="2" t="inlineStr"/>
-      <c r="H71" s="2" t="inlineStr">
+      <c r="G68" s="2" t="inlineStr"/>
+      <c r="H68" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -4049,39 +3898,39 @@
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C72" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="inlineStr">
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
         <is>
           <t>Mon, 17 Aug 2026 04:53:18 +0000</t>
         </is>
       </c>
-      <c r="E72" s="2" t="inlineStr">
+      <c r="E69" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F72" s="2" t="inlineStr">
+      <c r="F69" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G72" s="2" t="inlineStr"/>
-      <c r="H72" s="2" t="inlineStr">
+      <c r="G69" s="2" t="inlineStr"/>
+      <c r="H69" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -4097,39 +3946,39 @@
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="2" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C73" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D73" s="2" t="inlineStr">
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
         <is>
           <t>Sun, 16 Aug 2026 04:55:15 +0000</t>
         </is>
       </c>
-      <c r="E73" s="2" t="inlineStr">
+      <c r="E70" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F73" s="2" t="inlineStr">
+      <c r="F70" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G73" s="2" t="inlineStr"/>
-      <c r="H73" s="2" t="inlineStr">
+      <c r="G70" s="2" t="inlineStr"/>
+      <c r="H70" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -4145,39 +3994,39 @@
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="2" t="inlineStr">
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C74" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D74" s="2" t="inlineStr">
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
         <is>
           <t>Sun, 16 Aug 2026 02:33:51 +0000</t>
         </is>
       </c>
-      <c r="E74" s="2" t="inlineStr">
+      <c r="E71" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F74" s="2" t="inlineStr">
+      <c r="F71" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (TGTg3P+M9T)</t>
         </is>
       </c>
-      <c r="G74" s="2" t="inlineStr"/>
-      <c r="H74" s="2" t="inlineStr">
+      <c r="G71" s="2" t="inlineStr"/>
+      <c r="H71" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -4202,39 +4051,39 @@
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="2" t="inlineStr">
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C75" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="inlineStr">
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
         <is>
           <t>Sat, 15 Aug 2026 09:36:41 +0000</t>
         </is>
       </c>
-      <c r="E75" s="2" t="inlineStr">
+      <c r="E72" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F75" s="2" t="inlineStr">
+      <c r="F72" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G75" s="2" t="inlineStr"/>
-      <c r="H75" s="2" t="inlineStr">
+      <c r="G72" s="2" t="inlineStr"/>
+      <c r="H72" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -4250,39 +4099,39 @@
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr">
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C76" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D76" s="2" t="inlineStr">
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
         <is>
           <t>Sat, 15 Aug 2026 04:42:49 +0000</t>
         </is>
       </c>
-      <c r="E76" s="2" t="inlineStr">
+      <c r="E73" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F76" s="2" t="inlineStr">
+      <c r="F73" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G76" s="2" t="inlineStr"/>
-      <c r="H76" s="2" t="inlineStr">
+      <c r="G73" s="2" t="inlineStr"/>
+      <c r="H73" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -4298,39 +4147,39 @@
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="2" t="inlineStr">
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C77" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="inlineStr">
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
         <is>
           <t>Sat, 15 Aug 2026 01:29:59 +0000</t>
         </is>
       </c>
-      <c r="E77" s="2" t="inlineStr">
+      <c r="E74" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F77" s="2" t="inlineStr">
+      <c r="F74" s="2" t="inlineStr">
         <is>
           <t>Automated unfulfillable FBA inventory removal notification</t>
         </is>
       </c>
-      <c r="G77" s="2" t="inlineStr"/>
-      <c r="H77" s="2" t="inlineStr">
+      <c r="G74" s="2" t="inlineStr"/>
+      <c r="H74" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -4351,39 +4200,39 @@
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="2" t="inlineStr">
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C78" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D78" s="2" t="inlineStr">
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
         <is>
           <t>Thu, 13 Aug 2026 04:59:33 +0000</t>
         </is>
       </c>
-      <c r="E78" s="2" t="inlineStr">
+      <c r="E75" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F78" s="2" t="inlineStr">
+      <c r="F75" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G78" s="2" t="inlineStr"/>
-      <c r="H78" s="2" t="inlineStr">
+      <c r="G75" s="2" t="inlineStr"/>
+      <c r="H75" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -4399,39 +4248,39 @@
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" s="2" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C79" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D79" s="2" t="inlineStr">
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
         <is>
           <t>Wed, 12 Aug 2026 12:15:45 +0000</t>
         </is>
       </c>
-      <c r="E79" s="2" t="inlineStr">
+      <c r="E76" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F79" s="2" t="inlineStr">
+      <c r="F76" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (tynmf1KRa8)</t>
         </is>
       </c>
-      <c r="G79" s="2" t="inlineStr"/>
-      <c r="H79" s="2" t="inlineStr">
+      <c r="G76" s="2" t="inlineStr"/>
+      <c r="H76" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -4451,39 +4300,39 @@
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="2" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C80" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D80" s="2" t="inlineStr">
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
         <is>
           <t>Wed, 12 Aug 2026 05:20:43 +0000</t>
         </is>
       </c>
-      <c r="E80" s="2" t="inlineStr">
+      <c r="E77" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F80" s="2" t="inlineStr">
+      <c r="F77" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G80" s="2" t="inlineStr"/>
-      <c r="H80" s="2" t="inlineStr">
+      <c r="G77" s="2" t="inlineStr"/>
+      <c r="H77" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -4499,39 +4348,39 @@
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="2" t="inlineStr">
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C81" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D81" s="2" t="inlineStr">
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
         <is>
           <t>Tue, 11 Aug 2026 05:46:43 +0000</t>
         </is>
       </c>
-      <c r="E81" s="2" t="inlineStr">
+      <c r="E78" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F81" s="2" t="inlineStr">
+      <c r="F78" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (m4n18h8HiD)</t>
         </is>
       </c>
-      <c r="G81" s="2" t="inlineStr"/>
-      <c r="H81" s="2" t="inlineStr">
+      <c r="G78" s="2" t="inlineStr"/>
+      <c r="H78" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -4556,39 +4405,39 @@
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" s="2" t="inlineStr">
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C82" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="inlineStr">
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
         <is>
           <t>Tue, 11 Aug 2026 05:00:42 +0000</t>
         </is>
       </c>
-      <c r="E82" s="2" t="inlineStr">
+      <c r="E79" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F82" s="2" t="inlineStr">
+      <c r="F79" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G82" s="2" t="inlineStr"/>
-      <c r="H82" s="2" t="inlineStr">
+      <c r="G79" s="2" t="inlineStr"/>
+      <c r="H79" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -4604,39 +4453,39 @@
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" s="2" t="inlineStr">
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C83" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D83" s="2" t="inlineStr">
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
         <is>
           <t>Mon, 10 Aug 2026 09:16:35 +0000</t>
         </is>
       </c>
-      <c r="E83" s="2" t="inlineStr">
+      <c r="E80" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F83" s="2" t="inlineStr">
+      <c r="F80" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G83" s="2" t="inlineStr"/>
-      <c r="H83" s="2" t="inlineStr">
+      <c r="G80" s="2" t="inlineStr"/>
+      <c r="H80" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -4652,39 +4501,39 @@
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" s="2" t="inlineStr">
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C84" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D84" s="2" t="inlineStr">
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
         <is>
           <t>Sun, 9 Aug 2026 14:33:13 +0000</t>
         </is>
       </c>
-      <c r="E84" s="2" t="inlineStr">
+      <c r="E81" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;seller-notification@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F84" s="2" t="inlineStr">
+      <c r="F81" s="2" t="inlineStr">
         <is>
           <t>Balance paid on your Amazon seller account</t>
         </is>
       </c>
-      <c r="G84" s="2" t="inlineStr"/>
-      <c r="H84" s="2" t="inlineStr">
+      <c r="G81" s="2" t="inlineStr"/>
+      <c r="H81" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon Services.
  We have charged your credit card for $126.79 in an attempt to settle your Amazon seller account balance.
@@ -4700,39 +4549,39 @@
         </is>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" s="2" t="inlineStr">
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C85" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D85" s="2" t="inlineStr">
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
         <is>
           <t>Sun, 9 Aug 2026 04:49:49 +0000</t>
         </is>
       </c>
-      <c r="E85" s="2" t="inlineStr">
+      <c r="E82" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F85" s="2" t="inlineStr">
+      <c r="F82" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G85" s="2" t="inlineStr"/>
-      <c r="H85" s="2" t="inlineStr">
+      <c r="G82" s="2" t="inlineStr"/>
+      <c r="H82" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -4748,39 +4597,39 @@
         </is>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" s="2" t="inlineStr">
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C86" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D86" s="2" t="inlineStr">
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
         <is>
           <t>Sat, 8 Aug 2026 14:11:22 +0000</t>
         </is>
       </c>
-      <c r="E86" s="2" t="inlineStr">
+      <c r="E83" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F86" s="2" t="inlineStr">
+      <c r="F83" s="2" t="inlineStr">
         <is>
           <t>Automated unfulfillable FBA inventory removal notification</t>
         </is>
       </c>
-      <c r="G86" s="2" t="inlineStr"/>
-      <c r="H86" s="2" t="inlineStr">
+      <c r="G83" s="2" t="inlineStr"/>
+      <c r="H83" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -4801,39 +4650,39 @@
         </is>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" s="2" t="inlineStr">
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C87" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D87" s="2" t="inlineStr">
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
         <is>
           <t>Sat, 8 Aug 2026 05:00:20 +0000</t>
         </is>
       </c>
-      <c r="E87" s="2" t="inlineStr">
+      <c r="E84" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F87" s="2" t="inlineStr">
+      <c r="F84" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G87" s="2" t="inlineStr"/>
-      <c r="H87" s="2" t="inlineStr">
+      <c r="G84" s="2" t="inlineStr"/>
+      <c r="H84" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -4849,39 +4698,39 @@
         </is>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" s="2" t="inlineStr">
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C88" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D88" s="2" t="inlineStr">
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
         <is>
           <t>Fri, 7 Aug 2026 17:55:17 +0000</t>
         </is>
       </c>
-      <c r="E88" s="2" t="inlineStr">
+      <c r="E85" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F88" s="2" t="inlineStr">
+      <c r="F85" s="2" t="inlineStr">
         <is>
           <t>Automated unfulfillable FBA inventory removal notification</t>
         </is>
       </c>
-      <c r="G88" s="2" t="inlineStr"/>
-      <c r="H88" s="2" t="inlineStr">
+      <c r="G85" s="2" t="inlineStr"/>
+      <c r="H85" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -4902,39 +4751,39 @@
         </is>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" s="2" t="inlineStr">
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C89" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D89" s="2" t="inlineStr">
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
         <is>
           <t>Fri, 7 Aug 2026 04:52:01 +0000</t>
         </is>
       </c>
-      <c r="E89" s="2" t="inlineStr">
+      <c r="E86" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F89" s="2" t="inlineStr">
+      <c r="F86" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G89" s="2" t="inlineStr"/>
-      <c r="H89" s="2" t="inlineStr">
+      <c r="G86" s="2" t="inlineStr"/>
+      <c r="H86" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -4950,39 +4799,39 @@
         </is>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" s="2" t="inlineStr">
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C90" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D90" s="2" t="inlineStr">
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
         <is>
           <t>Thu, 6 Aug 2026 17:19:22 +0000</t>
         </is>
       </c>
-      <c r="E90" s="2" t="inlineStr">
+      <c r="E87" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F90" s="2" t="inlineStr">
+      <c r="F87" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (PLBovnqz6i)</t>
         </is>
       </c>
-      <c r="G90" s="2" t="inlineStr"/>
-      <c r="H90" s="2" t="inlineStr">
+      <c r="G87" s="2" t="inlineStr"/>
+      <c r="H87" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -5002,39 +4851,39 @@
         </is>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" s="2" t="inlineStr">
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C91" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D91" s="2" t="inlineStr">
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
         <is>
           <t>Thu, 6 Aug 2026 05:43:06 +0000</t>
         </is>
       </c>
-      <c r="E91" s="2" t="inlineStr">
+      <c r="E88" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F91" s="2" t="inlineStr">
+      <c r="F88" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G91" s="2" t="inlineStr"/>
-      <c r="H91" s="2" t="inlineStr">
+      <c r="G88" s="2" t="inlineStr"/>
+      <c r="H88" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -5050,39 +4899,39 @@
         </is>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" s="2" t="inlineStr">
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C92" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D92" s="2" t="inlineStr">
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
         <is>
           <t>Tue, 4 Aug 2026 04:57:39 +0000</t>
         </is>
       </c>
-      <c r="E92" s="2" t="inlineStr">
+      <c r="E89" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F92" s="2" t="inlineStr">
+      <c r="F89" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G92" s="2" t="inlineStr"/>
-      <c r="H92" s="2" t="inlineStr">
+      <c r="G89" s="2" t="inlineStr"/>
+      <c r="H89" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -5098,39 +4947,39 @@
         </is>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" s="2" t="inlineStr">
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C93" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D93" s="2" t="inlineStr">
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
         <is>
           <t>Mon, 3 Aug 2026 16:27:49 +0000</t>
         </is>
       </c>
-      <c r="E93" s="2" t="inlineStr">
+      <c r="E90" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F93" s="2" t="inlineStr">
+      <c r="F90" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (3rwPw0NlBZ)</t>
         </is>
       </c>
-      <c r="G93" s="2" t="inlineStr"/>
-      <c r="H93" s="2" t="inlineStr">
+      <c r="G90" s="2" t="inlineStr"/>
+      <c r="H90" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -5150,39 +4999,39 @@
         </is>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" s="2" t="inlineStr">
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C94" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D94" s="2" t="inlineStr">
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
         <is>
           <t>Mon, 3 Aug 2026 04:52:33 +0000</t>
         </is>
       </c>
-      <c r="E94" s="2" t="inlineStr">
+      <c r="E91" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F94" s="2" t="inlineStr">
+      <c r="F91" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G94" s="2" t="inlineStr"/>
-      <c r="H94" s="2" t="inlineStr">
+      <c r="G91" s="2" t="inlineStr"/>
+      <c r="H91" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -5198,39 +5047,39 @@
         </is>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" s="2" t="inlineStr">
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C95" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D95" s="2" t="inlineStr">
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
         <is>
           <t>Sun, 2 Aug 2026 04:46:25 +0000</t>
         </is>
       </c>
-      <c r="E95" s="2" t="inlineStr">
+      <c r="E92" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F95" s="2" t="inlineStr">
+      <c r="F92" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G95" s="2" t="inlineStr"/>
-      <c r="H95" s="2" t="inlineStr">
+      <c r="G92" s="2" t="inlineStr"/>
+      <c r="H92" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -5246,39 +5095,39 @@
         </is>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" s="2" t="inlineStr">
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C96" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D96" s="2" t="inlineStr">
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
         <is>
           <t>Sat, 1 Aug 2026 04:49:15 +0000</t>
         </is>
       </c>
-      <c r="E96" s="2" t="inlineStr">
+      <c r="E93" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F96" s="2" t="inlineStr">
+      <c r="F93" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G96" s="2" t="inlineStr"/>
-      <c r="H96" s="2" t="inlineStr">
+      <c r="G93" s="2" t="inlineStr"/>
+      <c r="H93" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -5294,39 +5143,39 @@
         </is>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" s="2" t="inlineStr">
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C97" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D97" s="2" t="inlineStr">
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
         <is>
           <t>Fri, 31 Jul 2026 09:23:20 +0000</t>
         </is>
       </c>
-      <c r="E97" s="2" t="inlineStr">
+      <c r="E94" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F97" s="2" t="inlineStr">
+      <c r="F94" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G97" s="2" t="inlineStr"/>
-      <c r="H97" s="2" t="inlineStr">
+      <c r="G94" s="2" t="inlineStr"/>
+      <c r="H94" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -5342,39 +5191,39 @@
         </is>
       </c>
     </row>
-    <row r="98">
-      <c r="A98" s="2" t="inlineStr">
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C98" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D98" s="2" t="inlineStr">
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
         <is>
           <t>Thu, 30 Jul 2026 19:42:31 +0000</t>
         </is>
       </c>
-      <c r="E98" s="2" t="inlineStr">
+      <c r="E95" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F98" s="2" t="inlineStr">
+      <c r="F95" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (YsvR7aqoWy)</t>
         </is>
       </c>
-      <c r="G98" s="2" t="inlineStr"/>
-      <c r="H98" s="2" t="inlineStr">
+      <c r="G95" s="2" t="inlineStr"/>
+      <c r="H95" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -5399,39 +5248,140 @@
         </is>
       </c>
     </row>
-    <row r="99">
-      <c r="A99" s="2" t="inlineStr">
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B99" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C99" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D99" s="2" t="inlineStr">
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>Sat, 22 Aug 2026 17:14:31 +0000</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>Tu pago está en camino</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr"/>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>96
+This title will display on mobile devices
+ ¡Enhorabuena! El pago está de camino y llegará pronto.
+ El pago está en camino
+Enhorabuena, Weihai EU. Tu pago está en camino y te llegará en un plazo de tres a cinco días.
+El 08/22/26 17:14 WEST, iniciamos una transferencia a tu método de pago (cuenta bancaria terminado en 229) por un importe de €
+ 646,15.
+ Si el importe es inferior a lo esperado, ten en cuenta las siguientes preguntas:
+ ¿Tienes saldo no disponible en tu cuenta de vendedor? Puede que hayamos reservado algo de dinero para posibles devoluciones, reclamaciones o reversiones de cargo de clientes. En este caso, el saldo de cierre de tu informe de pagos te mostrará el saldo no disponible en reserva.
+ ¿Cubren tus ventas las tarifas de Amazon y las devoluciones del periodo de liquidación? El importe del pago refleja las ventas que has hecho y las tarifas de venta aplicadas tanto a dichas ventas como a cualquier promoción o servicio que hayas utilizado. Te recomendamos que revises tu informe de pagos en "Informes" de Seller Central para conocer el saldo de cierre.
+Para más información sobre los informes de pagos en Seller Central, visita nuestro curso oficial.
+Te deseamos un éx</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>付款/资金类</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>Sat, 22 Aug 2026 17:14:20 +0000</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>Your payment is on the way</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr"/>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>96
+This title will display on mobile devices
+ Congratulations! Your payment is on the way and will arrive soon.
+ Disbursement Attempted
+Congratulations Weihai EU! Your payment is on the way and will arrive within three to five days.
+On 08/22/26 17:14 CEST, we initiated a transfer to your payment method (bank account ending in 229) in the amount of €
+ 397.48.
+ If the amount is less than expected, here are a few questions to consider:
+ Do you have an unavailable balance? Amazon might be reserving money to cover potential returns, claims, or chargebacks from buyers. If this is the case, the closing balance in your Payment Report will display the unavailable balance that is reserved.
+ Did your sales cover all fees and returns for this statement period? The payment amount reflects sales activities, selling fees, and fees for promotions or services. We recommend reviewing your Payment Report under the Reports tab in Seller Central to understand your closing balance.
+To learn more about Payment Reports in Seller Central, please visit our official course.
+We wish you continued success!
+Thank you for selling in the Amazon store,
+Amazon Services
+Help us improve your payment experience on Ama</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>付款/资金类</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
         <is>
           <t>Sat, 22 Aug 2026 12:13:14 +0000</t>
         </is>
       </c>
-      <c r="E99" s="2" t="inlineStr">
+      <c r="E98" s="2" t="inlineStr">
         <is>
           <t>Amazon Accelerate &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F99" s="2" t="inlineStr">
+      <c r="F98" s="2" t="inlineStr">
         <is>
           <t>Early-bird pricing ends Saturday, Aug. 29—Save $100 before it's full price</t>
         </is>
       </c>
-      <c r="G99" s="2" t="inlineStr"/>
-      <c r="H99" s="2" t="inlineStr">
+      <c r="G98" s="2" t="inlineStr"/>
+      <c r="H98" s="2" t="inlineStr">
         <is>
           <t>[Amazon logo](https://go.amazonsellerservices.com/e/229492/2026-08-19/7z596mz/6845766770/h/4MOe7WIB0iKog9ZJ2gooAw5JI3-zJ2xmrM13S4lZjTw)
 [Early-bird ending soon](https://go.amazonsellerservices.com/e/229492/-medium-email-utm-source-email/7z596n3/6845766770/h/4MOe7WIB0iKog9ZJ2gooAw5JI3-zJ2xmrM13S4lZjTw)
@@ -5447,40 +5397,40 @@
         </is>
       </c>
     </row>
-    <row r="100">
-      <c r="A100" s="2" t="inlineStr">
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C100" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D100" s="2" t="inlineStr">
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
         <is>
           <t>Fri, 21 Aug 2026 10:16:19 +0000</t>
         </is>
       </c>
-      <c r="E100" s="2" t="inlineStr">
+      <c r="E99" s="2" t="inlineStr">
         <is>
           <t>Amazon Accelerate &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F100" s="2" t="inlineStr">
+      <c r="F99" s="2" t="inlineStr">
         <is>
           <t>The fireside chat we teased is here. Early-bird pricing ends next
  week.</t>
         </is>
       </c>
-      <c r="G100" s="2" t="inlineStr"/>
-      <c r="H100" s="2" t="inlineStr">
+      <c r="G99" s="2" t="inlineStr"/>
+      <c r="H99" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">[Amazon logo](https://go.amazonsellerservices.com/e/229492/2026-08-17/7z58bwt/6843878552/h/i5ZL7d6_GwNwKOo6-EVWTgdYbnnn0rhnWQ2kP-UgsCs)
 [Partner Connect at Accelerate 2026](https://go.amazonsellerservices.com/e/229492/-medium-email-utm-source-email/7z58bwx/6843878552/h/i5ZL7d6_GwNwKOo6-EVWTgdYbnnn0rhnWQ2kP-UgsCs)
@@ -5496,39 +5446,39 @@
         </is>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" s="2" t="inlineStr">
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C101" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D101" s="2" t="inlineStr">
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
         <is>
           <t>Thu, 20 Aug 2026 16:05:40 +0000</t>
         </is>
       </c>
-      <c r="E101" s="2" t="inlineStr">
+      <c r="E100" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F101" s="2" t="inlineStr">
+      <c r="F100" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G101" s="2" t="inlineStr"/>
-      <c r="H101" s="2" t="inlineStr">
+      <c r="G100" s="2" t="inlineStr"/>
+      <c r="H100" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5548,39 +5498,39 @@
         </is>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" s="2" t="inlineStr">
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C102" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D102" s="2" t="inlineStr">
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
         <is>
           <t>Thu, 20 Aug 2026 16:03:47 +0000</t>
         </is>
       </c>
-      <c r="E102" s="2" t="inlineStr">
+      <c r="E101" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F102" s="2" t="inlineStr">
+      <c r="F101" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G102" s="2" t="inlineStr"/>
-      <c r="H102" s="2" t="inlineStr">
+      <c r="G101" s="2" t="inlineStr"/>
+      <c r="H101" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 This title will display on mobile devices
@@ -5597,39 +5547,39 @@
         </is>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" s="2" t="inlineStr">
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C103" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D103" s="2" t="inlineStr">
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
         <is>
           <t>Thu, 20 Aug 2026 16:03:34 +0000</t>
         </is>
       </c>
-      <c r="E103" s="2" t="inlineStr">
+      <c r="E102" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F103" s="2" t="inlineStr">
+      <c r="F102" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G103" s="2" t="inlineStr"/>
-      <c r="H103" s="2" t="inlineStr">
+      <c r="G102" s="2" t="inlineStr"/>
+      <c r="H102" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5649,39 +5599,39 @@
         </is>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" s="2" t="inlineStr">
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C104" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D104" s="2" t="inlineStr">
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
         <is>
           <t>Thu, 20 Aug 2026 12:23:03 +0000</t>
         </is>
       </c>
-      <c r="E104" s="2" t="inlineStr">
+      <c r="E103" s="2" t="inlineStr">
         <is>
           <t>Amazon Accelerate &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F104" s="2" t="inlineStr">
+      <c r="F103" s="2" t="inlineStr">
         <is>
           <t>You're exactly who Accelerate was designed for</t>
         </is>
       </c>
-      <c r="G104" s="2" t="inlineStr"/>
-      <c r="H104" s="2" t="inlineStr">
+      <c r="G103" s="2" t="inlineStr"/>
+      <c r="H103" s="2" t="inlineStr">
         <is>
           <t>[Amazon logo](https://go.amazonsellerservices.com/e/229492/2026-08-18/7z58zcm/6842423531/h/zqV8R_k6k7yKhqDq4dX1yXmefn5JIN40lXum5Y6M4KM)
 [Your next level starts here](https://go.amazonsellerservices.com/e/229492/-medium-email-utm-source-email/7z58zcq/6842423531/h/zqV8R_k6k7yKhqDq4dX1yXmefn5JIN40lXum5Y6M4KM)
@@ -5696,40 +5646,40 @@
         </is>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" s="2" t="inlineStr">
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B105" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C105" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D105" s="2" t="inlineStr">
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
         <is>
           <t>Tue, 18 Aug 2026 12:13:14 +0000</t>
         </is>
       </c>
-      <c r="E105" s="2" t="inlineStr">
+      <c r="E104" s="2" t="inlineStr">
         <is>
           <t>Amazon Accelerate &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F105" s="2" t="inlineStr">
+      <c r="F104" s="2" t="inlineStr">
         <is>
           <t>Live at Accelerate 2026: Mary Beth Westmoreland and Amit Agarwal
  fireside chat</t>
         </is>
       </c>
-      <c r="G105" s="2" t="inlineStr"/>
-      <c r="H105" s="2" t="inlineStr">
+      <c r="G104" s="2" t="inlineStr"/>
+      <c r="H104" s="2" t="inlineStr">
         <is>
           <t>[Amazon logo](https://go.amazonsellerservices.com/e/229492/2026-08-17/7z58bxx/6837257199/h/ROTGYDonH0Pvpb92J9CZAGdoz2-iazjSlqoOkDG1azg)
 [Partner Connect at Accelerate 2026](https://go.amazonsellerservices.com/e/229492/-medium-email-utm-source-email/7z58by1/6837257199/h/ROTGYDonH0Pvpb92J9CZAGdoz2-iazjSlqoOkDG1azg)
@@ -5742,39 +5692,39 @@
         </is>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" s="2" t="inlineStr">
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C106" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D106" s="2" t="inlineStr">
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
         <is>
           <t>Mon, 17 Aug 2026 18:27:13 +0000</t>
         </is>
       </c>
-      <c r="E106" s="2" t="inlineStr">
+      <c r="E105" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F106" s="2" t="inlineStr">
+      <c r="F105" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G106" s="2" t="inlineStr"/>
-      <c r="H106" s="2" t="inlineStr">
+      <c r="G105" s="2" t="inlineStr"/>
+      <c r="H105" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5791,39 +5741,39 @@
         </is>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" s="2" t="inlineStr">
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C107" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D107" s="2" t="inlineStr">
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
         <is>
           <t>Mon, 17 Aug 2026 18:26:45 +0000</t>
         </is>
       </c>
-      <c r="E107" s="2" t="inlineStr">
+      <c r="E106" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F107" s="2" t="inlineStr">
+      <c r="F106" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G107" s="2" t="inlineStr"/>
-      <c r="H107" s="2" t="inlineStr">
+      <c r="G106" s="2" t="inlineStr"/>
+      <c r="H106" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5843,39 +5793,39 @@
         </is>
       </c>
     </row>
-    <row r="108">
-      <c r="A108" s="2" t="inlineStr">
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C108" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D108" s="2" t="inlineStr">
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
         <is>
           <t>Sat, 15 Aug 2026 13:39:43 +0000</t>
         </is>
       </c>
-      <c r="E108" s="2" t="inlineStr">
+      <c r="E107" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F108" s="2" t="inlineStr">
+      <c r="F107" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G108" s="2" t="inlineStr"/>
-      <c r="H108" s="2" t="inlineStr">
+      <c r="G107" s="2" t="inlineStr"/>
+      <c r="H107" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5895,39 +5845,39 @@
         </is>
       </c>
     </row>
-    <row r="109">
-      <c r="A109" s="2" t="inlineStr">
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C109" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D109" s="2" t="inlineStr">
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
         <is>
           <t>Sat, 15 Aug 2026 13:38:59 +0000</t>
         </is>
       </c>
-      <c r="E109" s="2" t="inlineStr">
+      <c r="E108" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F109" s="2" t="inlineStr">
+      <c r="F108" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G109" s="2" t="inlineStr"/>
-      <c r="H109" s="2" t="inlineStr">
+      <c r="G108" s="2" t="inlineStr"/>
+      <c r="H108" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5944,39 +5894,39 @@
         </is>
       </c>
     </row>
-    <row r="110">
-      <c r="A110" s="2" t="inlineStr">
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C110" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D110" s="2" t="inlineStr">
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
         <is>
           <t>Fri, 14 Aug 2026 10:11:50 +0000</t>
         </is>
       </c>
-      <c r="E110" s="2" t="inlineStr">
+      <c r="E109" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F110" s="2" t="inlineStr">
+      <c r="F109" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G110" s="2" t="inlineStr"/>
-      <c r="H110" s="2" t="inlineStr">
+      <c r="G109" s="2" t="inlineStr"/>
+      <c r="H109" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5993,39 +5943,39 @@
         </is>
       </c>
     </row>
-    <row r="111">
-      <c r="A111" s="2" t="inlineStr">
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C111" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D111" s="2" t="inlineStr">
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
         <is>
           <t>Fri, 14 Aug 2026 10:11:23 +0000</t>
         </is>
       </c>
-      <c r="E111" s="2" t="inlineStr">
+      <c r="E110" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F111" s="2" t="inlineStr">
+      <c r="F110" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G111" s="2" t="inlineStr"/>
-      <c r="H111" s="2" t="inlineStr">
+      <c r="G110" s="2" t="inlineStr"/>
+      <c r="H110" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -6045,39 +5995,39 @@
         </is>
       </c>
     </row>
-    <row r="112">
-      <c r="A112" s="2" t="inlineStr">
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C112" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D112" s="2" t="inlineStr">
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
         <is>
           <t>Fri, 14 Aug 2026 07:03:07 +0000</t>
         </is>
       </c>
-      <c r="E112" s="2" t="inlineStr">
+      <c r="E111" s="2" t="inlineStr">
         <is>
           <t>Amazon Services Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F112" s="2" t="inlineStr">
+      <c r="F111" s="2" t="inlineStr">
         <is>
           <t>您的亚马逊卖家账户支付的余额</t>
         </is>
       </c>
-      <c r="G112" s="2" t="inlineStr"/>
-      <c r="H112" s="2" t="inlineStr">
+      <c r="G111" s="2" t="inlineStr"/>
+      <c r="H111" s="2" t="inlineStr">
         <is>
           <t>96
 您的亚马逊卖家账户支付的余额
@@ -6106,40 +6056,40 @@
         </is>
       </c>
     </row>
-    <row r="113">
-      <c r="A113" s="2" t="inlineStr">
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B113" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C113" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D113" s="2" t="inlineStr">
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
         <is>
           <t>Thu, 13 Aug 2026 13:25:55 +0000</t>
         </is>
       </c>
-      <c r="E113" s="2" t="inlineStr">
+      <c r="E112" s="2" t="inlineStr">
         <is>
           <t>Amazon Accelerate &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F113" s="2" t="inlineStr">
+      <c r="F112" s="2" t="inlineStr">
         <is>
           <t>Did you catch Mary Beth's message? Early-bird extension ends August
  29</t>
         </is>
       </c>
-      <c r="G113" s="2" t="inlineStr"/>
-      <c r="H113" s="2" t="inlineStr">
+      <c r="G112" s="2" t="inlineStr"/>
+      <c r="H112" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">[Amazon logo](https://go.amazonsellerservices.com/e/229492/2026-08-07/7z543yq/6828853872/h/09uV_tsw5XUFTzEZF_b-1pdSpEuhEDbCowtX9OlIcwk)
 [Partner Connect at Accelerate 2026](https://go.amazonsellerservices.com/e/229492/-medium-email-utm-source-email/7z543yt/6828853872/h/09uV_tsw5XUFTzEZF_b-1pdSpEuhEDbCowtX9OlIcwk)
@@ -6153,39 +6103,39 @@
         </is>
       </c>
     </row>
-    <row r="114">
-      <c r="A114" s="2" t="inlineStr">
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C114" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D114" s="2" t="inlineStr">
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
         <is>
           <t>Wed, 12 Aug 2026 15:01:57 +0000</t>
         </is>
       </c>
-      <c r="E114" s="2" t="inlineStr">
+      <c r="E113" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F114" s="2" t="inlineStr">
+      <c r="F113" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G114" s="2" t="inlineStr"/>
-      <c r="H114" s="2" t="inlineStr">
+      <c r="G113" s="2" t="inlineStr"/>
+      <c r="H113" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -6202,39 +6152,39 @@
         </is>
       </c>
     </row>
-    <row r="115">
-      <c r="A115" s="2" t="inlineStr">
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B115" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C115" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D115" s="2" t="inlineStr">
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
         <is>
           <t>Wed, 12 Aug 2026 15:01:21 +0000</t>
         </is>
       </c>
-      <c r="E115" s="2" t="inlineStr">
+      <c r="E114" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F115" s="2" t="inlineStr">
+      <c r="F114" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G115" s="2" t="inlineStr"/>
-      <c r="H115" s="2" t="inlineStr">
+      <c r="G114" s="2" t="inlineStr"/>
+      <c r="H114" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -6254,39 +6204,39 @@
         </is>
       </c>
     </row>
-    <row r="116">
-      <c r="A116" s="2" t="inlineStr">
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B116" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C116" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D116" s="2" t="inlineStr">
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
         <is>
           <t>Wed, 12 Aug 2026 13:10:07 +0000</t>
         </is>
       </c>
-      <c r="E116" s="2" t="inlineStr">
+      <c r="E115" s="2" t="inlineStr">
         <is>
           <t>Sell with Amazon &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F116" s="2" t="inlineStr">
+      <c r="F115" s="2" t="inlineStr">
         <is>
           <t>Hear from sellers who've been to Accelerate—92.9% of sellers said it was worth it</t>
         </is>
       </c>
-      <c r="G116" s="2" t="inlineStr"/>
-      <c r="H116" s="2" t="inlineStr">
+      <c r="G115" s="2" t="inlineStr"/>
+      <c r="H115" s="2" t="inlineStr">
         <is>
           <t>[Amazon logo](https://go.amazonsellerservices.com/e/229492/2026-08-11/7z56gp4/6826508754/h/QiUyqAFaZJ8bybuETp2Zaj1aeQqep5gBwkvyQ1nNdro)
 [Partner Connect at Accelerate 2026](https://go.amazonsellerservices.com/e/229492/-medium-email-utm-source-email/7z56gp7/6826508754/h/QiUyqAFaZJ8bybuETp2Zaj1aeQqep5gBwkvyQ1nNdro)
@@ -6301,39 +6251,39 @@
         </is>
       </c>
     </row>
-    <row r="117">
-      <c r="A117" s="2" t="inlineStr">
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B117" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C117" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D117" s="2" t="inlineStr">
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
         <is>
           <t>Tue, 11 Aug 2026 12:45:09 +0000</t>
         </is>
       </c>
-      <c r="E117" s="2" t="inlineStr">
+      <c r="E116" s="2" t="inlineStr">
         <is>
           <t>Amazon Accelerate &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F117" s="2" t="inlineStr">
+      <c r="F116" s="2" t="inlineStr">
         <is>
           <t>Mary Beth Westmoreland invites you to Amazon Accelerate 2026</t>
         </is>
       </c>
-      <c r="G117" s="2" t="inlineStr"/>
-      <c r="H117" s="2" t="inlineStr">
+      <c r="G116" s="2" t="inlineStr"/>
+      <c r="H116" s="2" t="inlineStr">
         <is>
           <t>[Amazon logo](https://go.amazonsellerservices.com/e/229492/2026-08-07/7z543zx/6824284947/h/IMGEB96CBgyW2DY04pRCmrOMWOWCmWx4Su6ckkT2afE)
 [Partner Connect at Accelerate 2026](https://go.amazonsellerservices.com/e/229492/-medium-email-utm-source-email/7z54411/6824284947/h/IMGEB96CBgyW2DY04pRCmrOMWOWCmWx4Su6ckkT2afE)
@@ -6346,39 +6296,39 @@
         </is>
       </c>
     </row>
-    <row r="118">
-      <c r="A118" s="2" t="inlineStr">
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B118" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C118" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D118" s="2" t="inlineStr">
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
         <is>
           <t>Tue, 11 Aug 2026 11:39:46 +0000</t>
         </is>
       </c>
-      <c r="E118" s="2" t="inlineStr">
+      <c r="E117" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F118" s="2" t="inlineStr">
+      <c r="F117" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G118" s="2" t="inlineStr"/>
-      <c r="H118" s="2" t="inlineStr">
+      <c r="G117" s="2" t="inlineStr"/>
+      <c r="H117" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 This title will display on mobile devices
@@ -6395,39 +6345,39 @@
         </is>
       </c>
     </row>
-    <row r="119">
-      <c r="A119" s="2" t="inlineStr">
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B119" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C119" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D119" s="2" t="inlineStr">
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
         <is>
           <t>Tue, 11 Aug 2026 11:39:19 +0000</t>
         </is>
       </c>
-      <c r="E119" s="2" t="inlineStr">
+      <c r="E118" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F119" s="2" t="inlineStr">
+      <c r="F118" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G119" s="2" t="inlineStr"/>
-      <c r="H119" s="2" t="inlineStr">
+      <c r="G118" s="2" t="inlineStr"/>
+      <c r="H118" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -6447,39 +6397,39 @@
         </is>
       </c>
     </row>
-    <row r="120">
-      <c r="A120" s="2" t="inlineStr">
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B120" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C120" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D120" s="2" t="inlineStr">
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
         <is>
           <t>Sun, 9 Aug 2026 14:20:11 +0000</t>
         </is>
       </c>
-      <c r="E120" s="2" t="inlineStr">
+      <c r="E119" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F120" s="2" t="inlineStr">
+      <c r="F119" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G120" s="2" t="inlineStr"/>
-      <c r="H120" s="2" t="inlineStr">
+      <c r="G119" s="2" t="inlineStr"/>
+      <c r="H119" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -6499,39 +6449,39 @@
         </is>
       </c>
     </row>
-    <row r="121">
-      <c r="A121" s="2" t="inlineStr">
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B121" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C121" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D121" s="2" t="inlineStr">
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
         <is>
           <t>Fri, 7 Aug 2026 23:31:39 +0000</t>
         </is>
       </c>
-      <c r="E121" s="2" t="inlineStr">
+      <c r="E120" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F121" s="2" t="inlineStr">
+      <c r="F120" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G121" s="2" t="inlineStr"/>
-      <c r="H121" s="2" t="inlineStr">
+      <c r="G120" s="2" t="inlineStr"/>
+      <c r="H120" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -6551,39 +6501,39 @@
         </is>
       </c>
     </row>
-    <row r="122">
-      <c r="A122" s="2" t="inlineStr">
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B122" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C122" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D122" s="2" t="inlineStr">
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
         <is>
           <t>Fri, 7 Aug 2026 15:18:33 +0000</t>
         </is>
       </c>
-      <c r="E122" s="2" t="inlineStr">
+      <c r="E121" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F122" s="2" t="inlineStr">
+      <c r="F121" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G122" s="2" t="inlineStr"/>
-      <c r="H122" s="2" t="inlineStr">
+      <c r="G121" s="2" t="inlineStr"/>
+      <c r="H121" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -6603,39 +6553,39 @@
         </is>
       </c>
     </row>
-    <row r="123">
-      <c r="A123" s="2" t="inlineStr">
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B123" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C123" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D123" s="2" t="inlineStr">
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
         <is>
           <t>Fri, 7 Aug 2026 15:18:03 +0000</t>
         </is>
       </c>
-      <c r="E123" s="2" t="inlineStr">
+      <c r="E122" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F123" s="2" t="inlineStr">
+      <c r="F122" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G123" s="2" t="inlineStr"/>
-      <c r="H123" s="2" t="inlineStr">
+      <c r="G122" s="2" t="inlineStr"/>
+      <c r="H122" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 This title will display on mobile devices
@@ -6652,39 +6602,39 @@
         </is>
       </c>
     </row>
-    <row r="124">
-      <c r="A124" s="2" t="inlineStr">
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B124" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C124" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D124" s="2" t="inlineStr">
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
         <is>
           <t>Fri, 7 Aug 2026 15:17:38 +0000</t>
         </is>
       </c>
-      <c r="E124" s="2" t="inlineStr">
+      <c r="E123" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F124" s="2" t="inlineStr">
+      <c r="F123" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G124" s="2" t="inlineStr"/>
-      <c r="H124" s="2" t="inlineStr">
+      <c r="G123" s="2" t="inlineStr"/>
+      <c r="H123" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -6704,39 +6654,39 @@
         </is>
       </c>
     </row>
-    <row r="125">
-      <c r="A125" s="2" t="inlineStr">
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B125" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C125" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D125" s="2" t="inlineStr">
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
         <is>
           <t>Thu, 6 Aug 2026 15:49:22 +0000</t>
         </is>
       </c>
-      <c r="E125" s="2" t="inlineStr">
+      <c r="E124" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;seller-notification@amazon.pl&gt;</t>
         </is>
       </c>
-      <c r="F125" s="2" t="inlineStr">
+      <c r="F124" s="2" t="inlineStr">
         <is>
           <t>Nieuregulowane saldo na koncie Amazon</t>
         </is>
       </c>
-      <c r="G125" s="2" t="inlineStr"/>
-      <c r="H125" s="2" t="inlineStr">
+      <c r="G124" s="2" t="inlineStr"/>
+      <c r="H124" s="2" t="inlineStr">
         <is>
           <t>Witamy!
  Masz na swoim koncie nieuregulowane saldo w wysokośc PLN 45.36. Obciążymy tą kwotą kartę kredytową zarejestrowaną jako metoda płatności dla Twojego konta
@@ -6750,39 +6700,39 @@
         </is>
       </c>
     </row>
-    <row r="126">
-      <c r="A126" s="2" t="inlineStr">
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B126" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C126" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D126" s="2" t="inlineStr">
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
         <is>
           <t>Thu, 6 Aug 2026 15:22:13 +0000</t>
         </is>
       </c>
-      <c r="E126" s="2" t="inlineStr">
+      <c r="E125" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F126" s="2" t="inlineStr">
+      <c r="F125" s="2" t="inlineStr">
         <is>
           <t>Rettifica del saldo negativo nei tuoi account</t>
         </is>
       </c>
-      <c r="G126" s="2" t="inlineStr"/>
-      <c r="H126" s="2" t="inlineStr">
+      <c r="G125" s="2" t="inlineStr"/>
+      <c r="H125" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -6806,39 +6756,39 @@
         </is>
       </c>
     </row>
-    <row r="127">
-      <c r="A127" s="2" t="inlineStr">
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B127" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C127" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D127" s="2" t="inlineStr">
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
         <is>
           <t>Tue, 4 Aug 2026 12:59:47 +0000</t>
         </is>
       </c>
-      <c r="E127" s="2" t="inlineStr">
+      <c r="E126" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F127" s="2" t="inlineStr">
+      <c r="F126" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G127" s="2" t="inlineStr"/>
-      <c r="H127" s="2" t="inlineStr">
+      <c r="G126" s="2" t="inlineStr"/>
+      <c r="H126" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -6855,39 +6805,39 @@
         </is>
       </c>
     </row>
-    <row r="128">
-      <c r="A128" s="2" t="inlineStr">
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B128" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C128" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D128" s="2" t="inlineStr">
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
         <is>
           <t>Mon, 3 Aug 2026 12:39:35 +0000</t>
         </is>
       </c>
-      <c r="E128" s="2" t="inlineStr">
+      <c r="E127" s="2" t="inlineStr">
         <is>
           <t>Amazon Accelerate &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F128" s="2" t="inlineStr">
+      <c r="F127" s="2" t="inlineStr">
         <is>
           <t>Final week of early-bird pricing for Amazon Accelerate 2026—ends August 8</t>
         </is>
       </c>
-      <c r="G128" s="2" t="inlineStr"/>
-      <c r="H128" s="2" t="inlineStr">
+      <c r="G127" s="2" t="inlineStr"/>
+      <c r="H127" s="2" t="inlineStr">
         <is>
           <t>[Amazon logo](https://go.amazonsellerservices.com/e/229492/2026-07-29/7z4ytv7/6806510535/h/ebUC-rn_gdmnOZgc0Tgqz8DiEn0AwvkMsQeazFirtjo)
 [Partner Connect at Accelerate 2026](https://go.amazonsellerservices.com/e/229492/-medium-email-utm-source-email/7z4ytvb/6806510535/h/ebUC-rn_gdmnOZgc0Tgqz8DiEn0AwvkMsQeazFirtjo)
@@ -6906,39 +6856,39 @@
         </is>
       </c>
     </row>
-    <row r="129">
-      <c r="A129" s="2" t="inlineStr">
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B129" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C129" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D129" s="2" t="inlineStr">
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
         <is>
           <t>Mon, 3 Aug 2026 12:14:10 +0000</t>
         </is>
       </c>
-      <c r="E129" s="2" t="inlineStr">
+      <c r="E128" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F129" s="2" t="inlineStr">
+      <c r="F128" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G129" s="2" t="inlineStr"/>
-      <c r="H129" s="2" t="inlineStr">
+      <c r="G128" s="2" t="inlineStr"/>
+      <c r="H128" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -6958,39 +6908,39 @@
         </is>
       </c>
     </row>
-    <row r="130">
-      <c r="A130" s="2" t="inlineStr">
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B130" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C130" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D130" s="2" t="inlineStr">
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
         <is>
           <t>Mon, 3 Aug 2026 12:13:54 +0000</t>
         </is>
       </c>
-      <c r="E130" s="2" t="inlineStr">
+      <c r="E129" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F130" s="2" t="inlineStr">
+      <c r="F129" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G130" s="2" t="inlineStr"/>
-      <c r="H130" s="2" t="inlineStr">
+      <c r="G129" s="2" t="inlineStr"/>
+      <c r="H129" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 This title will display on mobile devices
@@ -7007,39 +6957,39 @@
         </is>
       </c>
     </row>
-    <row r="131">
-      <c r="A131" s="2" t="inlineStr">
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B131" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C131" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D131" s="2" t="inlineStr">
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
         <is>
           <t>Mon, 3 Aug 2026 09:02:05 +0000</t>
         </is>
       </c>
-      <c r="E131" s="2" t="inlineStr">
+      <c r="E130" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F131" s="2" t="inlineStr">
+      <c r="F130" s="2" t="inlineStr">
         <is>
           <t>Managing compliance across Europe? There's a simpler way.</t>
         </is>
       </c>
-      <c r="G131" s="2" t="inlineStr"/>
-      <c r="H131" s="2" t="inlineStr">
+      <c r="G130" s="2" t="inlineStr"/>
+      <c r="H130" s="2" t="inlineStr">
         <is>
           <t>Managing compliance across Europe? There's a simpler way.
  96
@@ -7049,39 +6999,39 @@
         </is>
       </c>
     </row>
-    <row r="132">
-      <c r="A132" s="2" t="inlineStr">
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B132" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C132" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D132" s="2" t="inlineStr">
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
         <is>
           <t>Fri, 31 Jul 2026 12:51:30 +0000</t>
         </is>
       </c>
-      <c r="E132" s="2" t="inlineStr">
+      <c r="E131" s="2" t="inlineStr">
         <is>
           <t>Amazon Accelerate &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F132" s="2" t="inlineStr">
+      <c r="F131" s="2" t="inlineStr">
         <is>
           <t>Early-bird pricing ends August 8. Save $100 before the price goes up</t>
         </is>
       </c>
-      <c r="G132" s="2" t="inlineStr"/>
-      <c r="H132" s="2" t="inlineStr">
+      <c r="G131" s="2" t="inlineStr"/>
+      <c r="H131" s="2" t="inlineStr">
         <is>
           <t>[Amazon logo](https://go.amazonsellerservices.com/e/229492/2026-07-29/7z4ytt4/6801785250/h/cuj5ZID4pxnaoQxnGKVediz6maB8MtzjCTkMytKZvg4)
 [Partner Connect at Accelerate 2026](https://go.amazonsellerservices.com/e/229492/-medium-email-utm-source-email/7z4ytt7/6801785250/h/cuj5ZID4pxnaoQxnGKVediz6maB8MtzjCTkMytKZvg4)
@@ -7095,6 +7045,56 @@
 ​Build your schedule from 150+ sessions
 The full catalog is live across 11 topics. Register now to access the Agenda Builder and start favoriting sessions.
 Book your Seller Café appointm</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>产品链接/合规类</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
+        <is>
+          <t>Sat, 22 Aug 2026 23:14:29 +0000</t>
+        </is>
+      </c>
+      <c r="E132" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F132" s="2" t="inlineStr">
+        <is>
+          <t>Submit product safety documentation to reactivate listings</t>
+        </is>
+      </c>
+      <c r="G132" s="2" t="inlineStr"/>
+      <c r="H132" s="2" t="inlineStr">
+        <is>
+          <t>96
+ Submit product safety documentation to reactivate listings
+ Hello Weihai EU,
+ Some of your listings have been deactivated due to missing mandatory compliance requirements for your products. Review the details and next steps below. The affected listings are shown at the end of this email.
+ Why is this happening?
+ We are taking this action because these products are missing mandatory compliance information. Review our Product safety and compliance help page for information on applicable laws, regulations and Amazon policies. We leveraged a combination of automated means and expert human review to identify this issue and make this decision.
+ The table at the end of this email provides product-specific compliance requirements.
+ How do I reactivate my listing?
+ To provide the required compliance information, go to your Account Health page and locate the product compliance requests:
+-
+ If you have the required documentation, follow the instructions to submit your compliance documents. We will only reinstate products that fulfil the compliance requirements.
+-
+ If you believe that your products are exempt from these requirements, submit documentation demonstrating why they are not subj</t>
         </is>
       </c>
     </row>
